--- a/outputs/evaluation/requirement/validation/gemini-3-5-flash-lite/CF_M09/second/CF_M09_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-5-flash-lite/CF_M09/second/CF_M09_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.9833</v>
       </c>
       <c r="D13" t="n">
+        <v>0.9916</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9775</v>
       </c>
     </row>
@@ -755,14 +763,11 @@
           <t>The floor is assigned automatically or new ones can be created</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -776,14 +781,11 @@
           <t>The plant is automatically assigned or new ones can be created</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -814,14 +816,11 @@
           <t>All intervention information must be seen simply</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>R_37</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -835,14 +834,11 @@
           <t>You must see all the information of the intervention in a simple way</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>CF_M09_R37</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -873,14 +869,11 @@
           <t>To be able to finalize the intervention, all required information must be filled in</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_37</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -894,14 +887,11 @@
           <t>In order to complete the intervention, you will have to fill in all the required information</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M09_R37</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -932,10 +922,6 @@
           <t>Enter the 3D map ID</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -949,10 +935,6 @@
           <t>Introduce the ID of the 3D map</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -983,14 +965,11 @@
           <t>An intervention can only be deleted if it is not finished</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_34</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1004,14 +983,11 @@
           <t>An intervention can only be removed if it is not completed.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M09_R34</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1042,14 +1018,11 @@
           <t>All asset attributes and asset type attributes must be able to be added to the asset</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1063,14 +1036,11 @@
           <t>All asset and asset type attributes can be added to the asset.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1101,14 +1071,11 @@
           <t>The created spot is seen automatically</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1122,14 +1089,11 @@
           <t>The created spot is automatically displayed.</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1160,10 +1124,6 @@
           <t>Eliminate spots of a location</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1177,10 +1137,6 @@
           <t>Remove spots from a location</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1211,14 +1167,11 @@
           <t>You must be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_27</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1232,14 +1185,11 @@
           <t>You should be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M09_R27</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1270,14 +1220,11 @@
           <t>You must be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1291,14 +1238,11 @@
           <t>You should be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M09_R23</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1329,14 +1273,11 @@
           <t>You must be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1350,14 +1291,11 @@
           <t>You should be able to see the details of each asset</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CF_M09_R20</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1388,10 +1326,6 @@
           <t>Eliminate an intervention</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1405,10 +1339,6 @@
           <t>Remove an intervention</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1439,14 +1369,11 @@
           <t>The spot to which it is assigned can be modified</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1460,14 +1387,11 @@
           <t>You can change the spot it is assigned to</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M09_R15</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1498,14 +1422,11 @@
           <t>Assets outside the location cannot be displayed</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1519,14 +1440,11 @@
           <t>Assets cannot be displayed outside of the location</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M09_R23</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1557,14 +1475,11 @@
           <t>Assets outside the location cannot be displayed</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_20</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1578,14 +1493,11 @@
           <t>Assets cannot be displayed outside of the location</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M09_R20</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1616,14 +1528,11 @@
           <t>You must be able to choose the intervened assets</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1637,14 +1546,11 @@
           <t>It must be possible to choose the intervened assets.</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>CF_M09_R30</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1675,10 +1581,6 @@
           <t>Eliminate assets from a spot</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1692,10 +1594,6 @@
           <t>Remove assets from a spot</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1726,14 +1624,11 @@
           <t>Assets that are not in the location or that are already in an intervention must not be able to be included</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1747,14 +1642,11 @@
           <t>It should not be possible to include assets that are not in the location or that they are already in an intervention</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>CF_M09_R30</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1785,10 +1677,6 @@
           <t>See the assets that are distributed in a location</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1802,10 +1690,6 @@
           <t>View the assets that are distributed across a location</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1836,10 +1720,6 @@
           <t>See the history of interventions performed</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1853,10 +1733,6 @@
           <t>See the history of interventions carried out</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1887,14 +1763,11 @@
           <t>A new ID cannot be entered once assigned</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>R_18</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1908,14 +1781,11 @@
           <t>A new ID cannot be introduced once assigned.</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>CF_M09_R18</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1946,10 +1816,6 @@
           <t>See the assets that are distributed in a location in the form of a 3D map</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>FR</t>
@@ -1963,10 +1829,6 @@
           <t>View the assets that are distributed across a location in 3D map format</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1997,14 +1859,11 @@
           <t>The information must be the same as in the list view</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>R_23</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2018,14 +1877,11 @@
           <t>The information must be the same as in the view of list</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>CF_M09_R23</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2056,10 +1912,6 @@
           <t>Modify the information of an asset</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2073,10 +1925,6 @@
           <t>Modify asset information</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2107,14 +1955,11 @@
           <t>The registry must be able to be consulted at the location level or at the asset level</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>R_40</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2128,14 +1973,11 @@
           <t>It must be possible to consult the registry at the location level or at the asset level.</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>CF_M09_R40</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2166,14 +2008,11 @@
           <t>A name can be assigned to each spot</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2187,14 +2026,11 @@
           <t>Each spot can be assigned a name.</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2225,14 +2061,11 @@
           <t>No user can see assets they do not have (except administrators, who see all)</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>R_27</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2246,14 +2079,11 @@
           <t>No user can see assets they do not own (except administrators, who see all).</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>CF_M09_R27</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2284,14 +2114,11 @@
           <t>The spot is removed from the list automatically</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2305,14 +2132,11 @@
           <t>The spot is automatically removed from the list.</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>CF_M09_R05</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2343,14 +2167,11 @@
           <t>The intervention is removed from the list automatically</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>R_34</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2364,14 +2185,11 @@
           <t>The intervention is automatically removed from the list.</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>CF_M09_R34</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2402,10 +2220,6 @@
           <t>See all the assets I have available</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>FR</t>
@@ -2419,10 +2233,6 @@
           <t>View all the assets I have available</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2453,14 +2263,11 @@
           <t>The asset is removed from the list automatically</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2474,14 +2281,11 @@
           <t>The asset is automatically removed from the list.</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>CF_M09_R12</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2517,9 +2321,6 @@
           <t>C_03</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2543,8 +2344,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2575,14 +2374,11 @@
           <t>A spot cannot be deleted if it has assigned assets</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2596,14 +2392,11 @@
           <t>A spot cannot be deleted if it has assets assigned to it.</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>CF_M09_R05</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2634,14 +2427,11 @@
           <t>The serial number can be left blank, in which case it will be assigned at installation</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2655,14 +2445,11 @@
           <t>The serial number can be left blank, in which case it will be assigned during installation.</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2693,14 +2480,11 @@
           <t>Any user can access the platform at any time of the day, with the exception of scheduled updates.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>R_50</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2714,14 +2498,11 @@
           <t>Any user can access the platform at any time of day, except for scheduled updates.</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>CF_M09_R50</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2752,14 +2533,11 @@
           <t>The spot is assigned automatically, although you can decide which spot you want to assign it to</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2773,14 +2551,11 @@
           <t>The spot is automatically assigned, although you can decide which spot you want to assign</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2816,9 +2591,6 @@
           <t>C_07</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2842,8 +2614,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2879,9 +2649,6 @@
           <t>C_09</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
           <t>QR</t>
@@ -2905,8 +2672,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2937,14 +2702,11 @@
           <t>The interface can be understood by anyone who speaks one of the 7 languages and the default language is English.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>R_44</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -2958,14 +2720,11 @@
           <t>The interface can be understood by any person who speaks one of the 7 languages and the default language is English.</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>CF_M09_R44</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3001,9 +2760,6 @@
           <t>C_08</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3027,8 +2783,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3059,14 +2813,11 @@
           <t>Each asset will be associated with an action</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>R_30</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3080,14 +2831,11 @@
           <t>Each asset will be associated with an action.</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>CF_M09_R30</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3118,14 +2866,11 @@
           <t>Any attribute of the asset can be modified</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3139,14 +2884,11 @@
           <t>Any attribute of the asset can be modified.</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>CF_M09_R15</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3177,14 +2919,11 @@
           <t>An asset can only be deleted if it is not assigned to an intervention</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3198,14 +2937,11 @@
           <t>An asset can only be deleted if it is not assigned to an intervention.</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>CF_M09_R12</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3236,14 +2972,11 @@
           <t>The interface adapts to computer, tablet, and mobile screens.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>R_54</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3257,14 +2990,11 @@
           <t>The interface adapts to computer, tablet, and mobile screens.</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>CF_M09_R54</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3300,9 +3030,6 @@
           <t>C_04</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3326,8 +3053,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3363,9 +3088,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3389,8 +3111,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3421,10 +3141,6 @@
           <t>Create new spots in a location</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>FR</t>
@@ -3438,10 +3154,6 @@
           <t>Create new spots in a location</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3477,9 +3189,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3503,8 +3212,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3535,10 +3242,6 @@
           <t>Perform and complete an intervention</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
           <t>FR</t>
@@ -3552,10 +3255,6 @@
           <t>Perform and complete an intervention</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3586,10 +3285,6 @@
           <t>Create assets assigned to a spot</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
           <t>FR</t>
@@ -3603,10 +3298,6 @@
           <t>Create assets assigned to a spot</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3637,14 +3328,11 @@
           <t>The system responds to any user action in less than five seconds.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>R_48</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3658,14 +3346,11 @@
           <t>The system responds to any user action in less than five seconds.</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>CF_M09_R48</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3701,9 +3386,6 @@
           <t>C_05</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3727,8 +3409,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3764,9 +3444,6 @@
           <t>C_06</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
           <t>QR</t>
@@ -3790,8 +3467,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3822,14 +3497,11 @@
           <t>Users without permission cannot access to view and edit assets.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>R_56</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3843,14 +3515,11 @@
           <t>Users without permission cannot access to view and edit assets.</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>CF_M09_R56</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3881,14 +3550,11 @@
           <t>The platform scales dynamically with changes in simultaneous connections.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>R_52</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3902,14 +3568,11 @@
           <t>The platform scales dynamically with changes in simultaneous connections.</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>CF_M09_R52</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3940,14 +3603,11 @@
           <t>Technical users learn to use the platform's functionalities in less than 30 minutes.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>R_46</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -3961,14 +3621,11 @@
           <t>Technical users learn to use the platform's functionalities in less than 30 minutes.</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>CF_M09_R46</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3999,14 +3656,11 @@
           <t>All colors used in the interface correspond to those defined in the Waapiti color palette included in the platform code.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>R_42</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -4020,14 +3674,11 @@
           <t>All colors used in the interface correspond to those defined in the Waapiti color palette included in the platform code.</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>CF_M09_R42</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4058,14 +3709,11 @@
           <t>No user can see information beyond their own.</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>R_58</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -4079,14 +3727,11 @@
           <t>No user can see information beyond their own.</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>CF_M09_R58</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4117,10 +3762,6 @@
           <t>Create a new intervention</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
           <t>FR</t>
@@ -4134,10 +3775,6 @@
           <t>Create a new intervention</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
